--- a/app/assets/TiposGastos.xlsx
+++ b/app/assets/TiposGastos.xlsx
@@ -1,149 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rommel Jiménez\Documents\Vertiche\02-CajaChica\MACRO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34B9CC1-B25D-46F4-8C92-8AA3AE80A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="14496" xr2:uid="{1D357179-A46F-46A8-973C-D5356FC06C70}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$24</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
+    <t>CODIGO</t>
+  </si>
+  <si>
+    <t>TIPO_GASTO</t>
+  </si>
+  <si>
+    <t>Agua</t>
+  </si>
+  <si>
+    <t>Alimentos</t>
+  </si>
+  <si>
+    <t>Artículos De Limpieza</t>
+  </si>
+  <si>
+    <t>Bolsas</t>
+  </si>
+  <si>
+    <t>Energía Eléctrica</t>
+  </si>
+  <si>
+    <t>Equipo de Cómputo Menor</t>
+  </si>
+  <si>
+    <t>Equipo Menor</t>
+  </si>
+  <si>
+    <t>Extintores y Protección Civil</t>
+  </si>
+  <si>
+    <t>Hospedaje</t>
+  </si>
+  <si>
+    <t>Impuesto Hospedaje</t>
+  </si>
+  <si>
+    <t>Licencias y Permisos</t>
+  </si>
+  <si>
+    <t>Medicamentos</t>
+  </si>
+  <si>
+    <t>No Deducibles</t>
+  </si>
+  <si>
+    <t>Otros</t>
+  </si>
+  <si>
+    <t>Papelería</t>
+  </si>
+  <si>
+    <t>Paquetería y Mensajería</t>
+  </si>
+  <si>
+    <t>Pasajes y Taxis</t>
+  </si>
+  <si>
+    <t>Publicidad</t>
+  </si>
+  <si>
+    <t>Recolección De Basura</t>
+  </si>
+  <si>
     <t>Servicio de Agua</t>
   </si>
   <si>
-    <t>Papelería</t>
-  </si>
-  <si>
-    <t>Equipo Menor</t>
-  </si>
-  <si>
-    <t>Agua</t>
-  </si>
-  <si>
-    <t>Medicamentos</t>
-  </si>
-  <si>
-    <t>Bolsa</t>
-  </si>
-  <si>
-    <t>Otros</t>
-  </si>
-  <si>
-    <t>Publicidad</t>
-  </si>
-  <si>
-    <t>Licencias y Permisos</t>
+    <t>Trámites</t>
   </si>
   <si>
     <t>Trasportación</t>
   </si>
   <si>
-    <t>Hospedaje</t>
-  </si>
-  <si>
-    <t>Alimentos</t>
-  </si>
-  <si>
-    <t>Pasajes y taxis</t>
-  </si>
-  <si>
     <t>Vigilancia</t>
-  </si>
-  <si>
-    <t>Equipo de Computo Menor</t>
-  </si>
-  <si>
-    <t>No Deducibles</t>
-  </si>
-  <si>
-    <t>CODIGO</t>
-  </si>
-  <si>
-    <t>TIPO_GASTO</t>
-  </si>
-  <si>
-    <t>Tramites</t>
-  </si>
-  <si>
-    <t>Artículos De Limpieza</t>
-  </si>
-  <si>
-    <t>Recolección De Basura</t>
-  </si>
-  <si>
-    <t>Extintores y Protección Civil</t>
-  </si>
-  <si>
-    <t>Energía Eléctrica</t>
-  </si>
-  <si>
-    <t>Impuesto Hospedaje</t>
-  </si>
-  <si>
-    <t>Paquetería y Mensajería</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
       <color rgb="FF000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,25 +125,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B8B4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,11 +148,11 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -197,17 +160,17 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -217,7 +180,7 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -225,23 +188,23 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -251,45 +214,35 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -309,7 +262,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -319,44 +272,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -384,31 +337,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -436,23 +372,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -464,136 +383,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -615,56 +578,52 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C494F9-6E0B-4B5B-B669-ED378A23A321}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="21.21875" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.285714285714285" customWidth="1"/>
+    <col min="2" max="2" width="23.285714285714285" customWidth="1"/>
+    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>601009</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>601157</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>601006</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>601013</v>
       </c>
@@ -672,119 +631,119 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>601003</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>601180</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>601008</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
         <v>601145</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
         <v>601154</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
         <v>601159</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
         <v>601124</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>601011</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
         <v>601264</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>601014</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
-        <v>601014</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>601007</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
         <v>601146</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>601158</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>601102</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>601010</v>
       </c>
@@ -792,47 +751,45 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>601005</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
         <v>601123</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="B22" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
         <v>601153</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>601173</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B24" xr:uid="{F4C494F9-6E0B-4B5B-B669-ED378A23A321}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B24">
-      <sortCondition ref="B1:B24"/>
+  <autoFilter ref="A1:B24">
+    <sortState ref="A1:B24">
+      <sortCondition ref="B2:B24"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B21">
-    <sortCondition ref="A2:A21"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>